--- a/uploads/Bid_file_success_error_newly_updated.xlsx
+++ b/uploads/Bid_file_success_error_newly_updated.xlsx
@@ -540,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>TestSigma_13-03-2026_SC1_60_613</v>
+        <v>TestSigma_16-03-2026_SC1_HG_319</v>
       </c>
       <c r="B2" s="1">
         <v>2001</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>TestSigma_13-03-2026_SC1_BO_348</v>
+        <v>TestSigma_16-03-2026_SC1_49_248</v>
       </c>
       <c r="B3" s="1">
         <v>2001</v>
@@ -768,7 +768,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>TestSigma_13-03-2026_SC1_RU_331</v>
+        <v>TestSigma_16-03-2026_SC1_O9_300</v>
       </c>
       <c r="B4" s="1">
         <v>2001</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>TestSigma_13-03-2026_SC1_YF_514</v>
+        <v>TestSigma_16-03-2026_SC1_CA_197</v>
       </c>
       <c r="B5" s="1">
         <v>2001</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>TestSigma_13-03-2026_SC1_GJ_777</v>
+        <v>TestSigma_16-03-2026_SC1_40_785</v>
       </c>
       <c r="B6" s="1">
         <v>2001</v>
@@ -1107,12 +1107,12 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>TestSigma_13-03-2026_SC1_3O_325</v>
+        <v>TestSigma_16-03-2026_SC1_6P_482</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v xml:space="preserve"> </v>
+        <v>TestSigma_16-03-2026_SC1_S9_900</v>
       </c>
     </row>
   </sheetData>
